--- a/abs_fpi/abs_fpi_internal.xlsx
+++ b/abs_fpi/abs_fpi_internal.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -146,6 +146,21 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -623,183 +638,183 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>abs_fpi_internal.xlsx —— 参数填写与代码生成说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="inlineStr"/>
+      <c r="A2" s="55" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="56" t="inlineStr">
         <is>
           <t>这个工作簿怎么用</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  1.  Global Parameter 的 B 列：全局变量取值（所有 Case 共用）。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  2.  Local Parameter 从 E 列起：每个 Case 一列，右拉复制即可增加。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  3.  改完参数后回到命令行执行：</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x abs_fpi_internal.xlsx --write-excel</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">      只想导出代码文件就换成 --outdir &lt;目录&gt;；只预览不写回则什么参数都不加。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr"/>
+      <c r="A10" s="55" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>★  部分输出表是公式（engine: excel）：改参数后 Excel 打开即重算，不用跑脚本</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   公式只做「占位符替换」；要生成代码文件（--outdir）或做 CI 检查（check）仍需命令行。</t>
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   公式支持占位符替换与行内分支（{% if %}）；要生成代码文件（--outdir）或做 CI 检查（check）仍需命令行。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">   不带 --write-excel 的 render 只预览，不会改变本文件。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr"/>
+      <c r="A14" s="55" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>输出位置</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  genie_int: Code @ B2 (horizontal)［公式·自动重算］</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  int_summary: Summary @ B2 (vertical)［公式·自动重算］</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Template（隐藏）：模板原文，只读参考，改它不影响渲染结果。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="inlineStr"/>
+      <c r="A19" s="55" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>本次生成</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  时间        2026-09-24 17:00:47</t>
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  时间        2026-09-27 15:22:53</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  输出指纹      99a08868664e</t>
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  输出指纹      c236aefb8f52</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="inlineStr">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  参数指纹      4dc57fc8ae2d</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  case 数    4</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="inlineStr">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  cases     WBT6-d8-mu90, WBT6-d15.059-mu0, WBT7-d20.559-mu90, COT1-d20.559-mu60</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  命令      python build.py  (abs_fpi_internal.yaml)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="inlineStr"/>
+      <c r="A27" s="55" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="51" t="inlineStr">
+      <c r="A28" s="56" t="inlineStr">
         <is>
           <t>工况一览（来自上一次渲染）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="inlineStr">
+      <c r="A29" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  WBT6-d8-mu90, WBT6-d15.059-mu0, WBT7-d20.559-mu90, COT1-d20.559-mu60</t>
         </is>
@@ -4359,7 +4374,7 @@
         <v/>
       </c>
       <c r="F2">
-        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本工具无舱作用域，数据按工况摊平） |"</f>
+        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本项目当前按工况摊平；工具 0.7.0 起支持成员表） |"</f>
         <v/>
       </c>
       <c r="G2">
@@ -4486,7 +4501,7 @@
         <v/>
       </c>
       <c r="F3">
-        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本工具无舱作用域，数据按工况摊平） |"</f>
+        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本项目当前按工况摊平；工具 0.7.0 起支持成员表） |"</f>
         <v/>
       </c>
       <c r="G3">
@@ -4613,7 +4628,7 @@
         <v/>
       </c>
       <c r="F4">
-        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本工具无舱作用域，数据按工况摊平） |"</f>
+        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本项目当前按工况摊平；工具 0.7.0 起支持成员表） |"</f>
         <v/>
       </c>
       <c r="G4">
@@ -4740,7 +4755,7 @@
         <v/>
       </c>
       <c r="F5">
-        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本工具无舱作用域，数据按工况摊平） |"</f>
+        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本项目当前按工况摊平；工具 0.7.0 起支持成员表） |"</f>
         <v/>
       </c>
       <c r="G5">
@@ -6600,7 +6615,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-24 17:00:47</t>
+          <t>2026-09-27 15:22:53</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6627,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>99a08868664e</t>
+          <t>c236aefb8f52</t>
         </is>
       </c>
     </row>

--- a/abs_fpi/abs_fpi_internal.xlsx
+++ b/abs_fpi/abs_fpi_internal.xlsx
@@ -10,9 +10,10 @@
     <sheet name="HOWTO" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Global Parameter" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Local Parameter" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Code" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Template" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Tank Data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Code" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Template" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -130,35 +131,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -176,81 +149,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -340,6 +239,470 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel_codegen</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>规范船长 [m]（3-1-1/3）
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：340
+模板里引用：{{ L }}</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>规范型宽 [m]
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：64
+模板里引用：{{ B }}</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>规范型深 [m]
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：32
+模板里引用：{{ D }}</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>结构吃水 [m]；规范表按它给出，GM 四点表也按它插值
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：20.559
+模板里引用：{{ d_f }}</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>海水密度 [kg/m^3]
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：float
+前缀 / 后缀：'' / ' kg/m^3'
+默认值：1025
+模板里引用：{{ rho_sea }}</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>重力加速度 [m/s^2]
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：float
+前缀 / 后缀：'' / ' m/s^2'
+默认值：9.81
+模板里引用：{{ g }}</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>方形系数 [-]
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：float
+默认值：1
+模板里引用：{{ Cb }}</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>k_s = 0.878 对应的 rho g [N/m^3]（1.005 N/cm^2-m = 10050）
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：float
+前缀 / 后缀：'' / ' N/m^3'
+默认值：10050
+模板里引用：{{ rho_g_lo }}</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>k_s 达到 1.0 的 rho g [N/m^3]（1.118 N/cm^2-m = 11180）
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：float
+前缀 / 后缀：'' / ' N/m^3'
+默认值：11180
+模板里引用：{{ rho_g_hi }}</t>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>规范 x（自 AP）取自模型哪个轴：1=x, 2=y, 3=z
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：string
+默认值：1
+模板里引用：{{ ax_x }}</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>规范 y（自中线，向右舷为正）取自模型哪个轴
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：string
+默认值：2
+模板里引用：{{ ax_y }}</t>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0">
+      <text>
+        <t>规范 z（基线以上，向上为正）取自模型哪个轴
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：string
+默认值：3
+模板里引用：{{ ax_z }}</t>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0" shapeId="0">
+      <text>
+        <t>规范 x 是否取反：填 - 表示取反，留空表示不取反
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：string
+模板里引用：{{ neg_x }}</t>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0" shapeId="0">
+      <text>
+        <t>规范 y 是否取反：填 - 表示取反，留空表示不取反
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：string
+模板里引用：{{ neg_y }}</t>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0">
+      <text>
+        <t>规范 z 是否取反：填 - 表示取反，留空表示不取反
+填写位置：Global 表 B 列（所有 Case 共用）
+类型：string
+模板里引用：{{ neg_z }}</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel_codegen</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>这个 Case 属于哪一套规则：EXT / INT（多规则集合用时用 case_filter 分流）
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：string
+默认值：INT
+模板里引用：{{ kind }}</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>工况吃水 [m]
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：8
+模板里引用：{{ draft }}</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>浪向角 [deg]（Table 1A D）
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+前缀 / 后缀：'' / ' deg'
+默认值：90
+模板里引用：{{ mu_deg }}</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>组合工况相关系数 [-]（Table 1A C）
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：1
+模板里引用：{{ k_c }}</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>载荷系数 [-]
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：1.1
+模板里引用：{{ k_u }}</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>垂向加速度 ESF [-]（5A-3-A1/3）
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：0.66
+模板里引用：{{ beta_VAC }}</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>纵向加速度 ESF [-]
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：0.758
+模板里引用：{{ beta_LAC }}</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>横向加速度 ESF [-]
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：0.557
+模板里引用：{{ beta_TAC }}</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>纵摇 ESF [-]
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：0.686
+模板里引用：{{ beta_PMO }}</t>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>横摇 ESF [-]
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：0.492
+模板里引用：{{ beta_RMO }}</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>项目对 ESF 的分项系数 [-]
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：1.1
+模板里引用：{{ k_esf }}</t>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0">
+      <text>
+        <t>垂向加速度权重 [-]（Table 1A B）
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：0.75
+模板里引用：{{ w_v }}</t>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0" shapeId="0">
+      <text>
+        <t>纵向加速度权重 [-]
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：0.25
+模板里引用：{{ w_l }}</t>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0" shapeId="0">
+      <text>
+        <t>横向加速度权重 [-]
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+默认值：0.75
+模板里引用：{{ w_t }}</t>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0">
+      <text>
+        <t>舱长方向参考位置 [m]（5.7.2(b)）
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：21
+模板里引用：{{ xi }}</t>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0">
+      <text>
+        <t>舱宽方向修正 [m]（5.7.2(b)）；无则填 0
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：0
+模板里引用：{{ delta_b }}</t>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0" shapeId="0">
+      <text>
+        <t>舱高方向修正 [m]（5.7.2(b)）；无则填 0
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：0
+模板里引用：{{ delta_h }}</t>
+      </text>
+    </comment>
+    <comment ref="A19" authorId="0" shapeId="0">
+      <text>
+        <t>本 Case 用哪个舱（成员表的行名）
+填写位置：Local 表 E 列起（一个 Case 一列）
+类型：string
+约束：可选: WBT6 / WBT7 / COT1
+默认值：WBT6
+模板里引用：{{ tank_ref }}</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel_codegen</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>舱内液体密度 [kg/m^3]
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+前缀 / 后缀：'' / ' kg/m^3'
+默认值：1025
+模板里引用：{{ rho_tank }}</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>舱长 [m]（Fig. 11）
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：42
+模板里引用：{{ l_tank }}</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>舱宽 [m]（Fig. 11）
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：32
+模板里引用：{{ b_tank }}</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>舱高 [m]（Fig. 11）
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：32
+模板里引用：{{ h_tank }}</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>甲板以上高度 [m]
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：0
+模板里引用：{{ eta_deck }}</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>溢流管高度 [m]；Fig. 12 要求取 2/3 且不低于 760 mm
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：0
+模板里引用：{{ eta_overflow }}</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>舱形系数 [-]（5.7.2(d)）：矩形 1.0，J 形 0.7
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+默认值：1
+模板里引用：{{ C_dp }}</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>舱形系数 [-]（5.7.2(d)）：矩形 1.0，U 形 0.7
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+默认值：1
+模板里引用：{{ C_ru }}</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>真空/压力阀整定压力 [N/cm^2]
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+前缀 / 后缀：'' / ' N/cm^2'
+默认值：0
+模板里引用：{{ p_vp }}</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>完整稳性 GM [m]；填 0 时用规范估算 0.12 B
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：0
+模板里引用：{{ GM_full_in }}</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>横摇惯性半径 [m]；填 0 时用规范估算（0.35 B / 0.45 B）
+填写位置：成员表（Tank Data）：一行一个成员
+类型：float
+前缀 / 后缀：'' / ' m'
+默认值：0
+模板里引用：{{ k_r_in }}</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>压载舱 1 / 货舱 0；决定 k_s 是否取 1
+填写位置：成员表（Tank Data）：一行一个成员
+类型：int
+默认值：1
+模板里引用：{{ tank_is_ballast }}</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>构件是否属于 5.7 表 3 的 11..17 项（1 = 是）
+填写位置：成员表（Tank Data）：一行一个成员
+类型：int
+默认值：0
+模板里引用：{{ member_11_17 }}</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -631,190 +994,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>abs_fpi_internal.xlsx —— 参数填写与代码生成说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="55" t="inlineStr"/>
+      <c r="A2" s="21" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="56" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>这个工作簿怎么用</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="55" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  1.  Global Parameter 的 B 列：全局变量取值（所有 Case 共用）。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  2.  Local Parameter 从 E 列起：每个 Case 一列，右拉复制即可增加。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  3.  改完参数后回到命令行执行：</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x abs_fpi_internal.xlsx --write-excel</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">      只想导出代码文件就换成 --outdir &lt;目录&gt;；只预览不写回则什么参数都不加。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ★ 懒得开终端就双击本文件旁边的 abs_fpi_internal_render.bat（Windows）或跑 abs_fpi_internal_render.sh（Linux / macOS）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="55" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="56" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>★  部分输出表是公式（engine: excel）：改参数后 Excel 打开即重算，不用跑脚本</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="55" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">   公式支持占位符替换与行内分支（{% if %}）；要生成代码文件（--outdir）或做 CI 检查（check）仍需命令行。</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="55" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">   不带 --write-excel 的 render 只预览，不会改变本文件。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="55" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="56" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>输出位置</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="58" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  genie_int: Code @ B2 (horizontal)［公式·自动重算］</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="58" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  int_summary: Summary @ B2 (vertical)［公式·自动重算］</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="55" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Template（隐藏）：模板原文，只读参考，改它不影响渲染结果。</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="55" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="56" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>本次生成</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  时间        2026-09-27 15:22:53</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  输出指纹      c236aefb8f52</t>
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  时间        2026-09-27 16:02:21</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  参数指纹      4dc57fc8ae2d</t>
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  输出指纹      89e5e9a6cff2</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  参数指纹      83967e51cf00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  case 数    4</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="55" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  cases     WBT6-d8-mu90, WBT6-d15.059-mu0, WBT7-d20.559-mu90, COT1-d20.559-mu60</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="58" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  命令      python build.py  (abs_fpi_internal.yaml)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="55" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="56" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>工况一览（来自上一次渲染）</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="58" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  WBT6-d8-mu90, WBT6-d15.059-mu0, WBT7-d20.559-mu90, COT1-d20.559-mu60</t>
         </is>
@@ -874,7 +1244,7 @@
           <t>L</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="13" t="n">
         <v>340</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -894,7 +1264,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="13" t="n">
         <v>64</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -914,7 +1284,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="13" t="n">
         <v>32</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -934,7 +1304,7 @@
           <t>d_f</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="13" t="n">
         <v>20.559</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,7 +1324,7 @@
           <t>rho_sea</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>1025</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -974,7 +1344,7 @@
           <t>g</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <v>9.81</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -994,7 +1364,7 @@
           <t>Cb</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -1009,7 +1379,7 @@
           <t>rho_g_lo</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>10050</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -1029,7 +1399,7 @@
           <t>rho_g_hi</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>11180</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -1049,7 +1419,7 @@
           <t>ax_x</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1066,7 +1436,7 @@
           <t>ax_y</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1083,7 +1453,7 @@
           <t>ax_z</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1100,7 +1470,7 @@
           <t>neg_x</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr"/>
+      <c r="B14" s="13" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>规范 x 是否取反：填 - 表示取反，留空表示不取反</t>
@@ -1113,7 +1483,7 @@
           <t>neg_y</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr"/>
+      <c r="B15" s="13" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>规范 y 是否取反：填 - 表示取反，留空表示不取反</t>
@@ -1126,7 +1496,7 @@
           <t>neg_z</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr"/>
+      <c r="B16" s="13" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>规范 z 是否取反：填 - 表示取反，留空表示不取反</t>
@@ -1135,6 +1505,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1144,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1210,22 +1581,22 @@
           <t>这个 Case 属于哪一套规则：EXT / INT（多规则集合用时用 case_filter 分流）</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
@@ -1247,16 +1618,16 @@
           <t xml:space="preserve"> m</t>
         </is>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="12" t="n">
+      <c r="F3" s="13" t="n">
         <v>15.059</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="13" t="n">
         <v>20.559</v>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="H3" s="13" t="n">
         <v>20.559</v>
       </c>
     </row>
@@ -1276,16 +1647,16 @@
           <t xml:space="preserve"> deg</t>
         </is>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="13" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1300,16 +1671,16 @@
           <t>组合工况相关系数 [-]（Table 1A C）</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="13" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1324,16 +1695,16 @@
           <t>载荷系数 [-]</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="13" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -1348,16 +1719,16 @@
           <t>垂向加速度 ESF [-]（5A-3-A1/3）</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <v>0.66</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="13" t="n">
         <v>0.66</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.66</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1372,16 +1743,16 @@
           <t>纵向加速度 ESF [-]</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <v>0.758</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="13" t="n">
         <v>0.758</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.758</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.758</v>
       </c>
     </row>
@@ -1396,16 +1767,16 @@
           <t>横向加速度 ESF [-]</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="13" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.5570000000000001</v>
       </c>
     </row>
@@ -1420,16 +1791,16 @@
           <t>纵摇 ESF [-]</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="13" t="n">
         <v>0.6860000000000001</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="13" t="n">
         <v>0.6860000000000001</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.6860000000000001</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.6860000000000001</v>
       </c>
     </row>
@@ -1444,16 +1815,16 @@
           <t>横摇 ESF [-]</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <v>0.492</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="13" t="n">
         <v>0.492</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.492</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.492</v>
       </c>
     </row>
@@ -1468,16 +1839,16 @@
           <t>项目对 ESF 的分项系数 [-]</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="13" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -1492,16 +1863,16 @@
           <t>垂向加速度权重 [-]（Table 1A B）</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1516,16 +1887,16 @@
           <t>纵向加速度权重 [-]</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1540,16 +1911,16 @@
           <t>横向加速度权重 [-]</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1569,16 +1940,16 @@
           <t xml:space="preserve"> m</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="13" t="n">
         <v>7.25</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" s="13" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1598,16 +1969,16 @@
           <t xml:space="preserve"> m</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="H17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1627,16 +1998,16 @@
           <t xml:space="preserve"> m</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H18" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1648,393 +2019,283 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>本列数据来自哪个舱（仅标注；样例 WBT6 / WBT7 / COT1）</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
+          <t>本 Case 用哪个舱（成员表的行名）</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>WBT6</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>WBT6</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>WBT7</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>COT1</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>rho_tank</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>舱内液体密度 [kg/m^3]</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> kg/m^3</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>1025</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>1025</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>1025</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>l_tank</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>舱长 [m]（Fig. 11）</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> m</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>b_tank</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>舱宽 [m]（Fig. 11）</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> m</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>h_tank</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>舱高 [m]（Fig. 11）</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> m</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>eta_deck</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>甲板以上高度 [m]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> m</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>eta_overflow</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>溢流管高度 [m]；Fig. 12 要求取 2/3 且不低于 760 mm</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> m</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C_dp</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>舱形系数 [-]（5.7.2(d)）：矩形 1.0，J 形 0.7</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>C_ru</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>舱形系数 [-]（5.7.2(d)）：矩形 1.0，U 形 0.7</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>p_vp</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>真空/压力阀整定压力 [N/cm^2]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> N/cm^2</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>GM_full_in</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>完整稳性 GM [m]；填 0 时用规范估算 0.12 B</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> m</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>k_r_in</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>横摇惯性半径 [m]；填 0 时用规范估算（0.35 B / 0.45 B）</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> m</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>tank_is_ballast</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>压载舱 1 / 货舱 0；决定 k_s 是否取 1</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>member_11_17</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>构件是否属于 5.7 表 3 的 11..17 项（1 = 是）</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E19 F19 G19 H19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="取值不合规" error="tank_ref：可选: WBT6 / WBT7 / COT1" promptTitle="tank_ref" prompt="可选: WBT6 / WBT7 / COT1" type="list">
+      <formula1>"WBT6,WBT7,COT1"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>成员</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>rho_tank</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>l_tank</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>b_tank</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>h_tank</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>eta_deck</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>eta_overflow</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>C_dp</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>C_ru</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>p_vp</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>GM_full_in</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>k_r_in</t>
+        </is>
+      </c>
+      <c r="M1" s="8" t="inlineStr">
+        <is>
+          <t>tank_is_ballast</t>
+        </is>
+      </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
+          <t>member_11_17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WBT6</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="n">
+        <v>1025</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WBT7</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>1025</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>COT1</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2050,22 +2311,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>WBT6-d8-mu90</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>WBT6-d15.059-mu0</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>WBT7-d20.559-mu90</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>COT1-d20.559-mu60</t>
         </is>
@@ -2721,235 +2982,235 @@
     </row>
     <row r="38">
       <c r="B38">
-        <f>"var rho_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),1025,IF(INDEX('Local Parameter'!E:E,MATCH("rho_tank",'Local Parameter'!$A:$A,0))="",1025,INDEX('Local Parameter'!E:E,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))," kg/m^3",IF(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))=""," kg/m^3",INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var rho_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1025,IF(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1025,INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" kg/m^3"&amp;";"</f>
         <v/>
       </c>
       <c r="C38">
-        <f>"var rho_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),1025,IF(INDEX('Local Parameter'!F:F,MATCH("rho_tank",'Local Parameter'!$A:$A,0))="",1025,INDEX('Local Parameter'!F:F,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))," kg/m^3",IF(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))=""," kg/m^3",INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var rho_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1025,IF(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1025,INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" kg/m^3"&amp;";"</f>
         <v/>
       </c>
       <c r="D38">
-        <f>"var rho_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),1025,IF(INDEX('Local Parameter'!G:G,MATCH("rho_tank",'Local Parameter'!$A:$A,0))="",1025,INDEX('Local Parameter'!G:G,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))," kg/m^3",IF(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))=""," kg/m^3",INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var rho_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1025,IF(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1025,INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" kg/m^3"&amp;";"</f>
         <v/>
       </c>
       <c r="E38">
-        <f>"var rho_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),1025,IF(INDEX('Local Parameter'!H:H,MATCH("rho_tank",'Local Parameter'!$A:$A,0))="",1025,INDEX('Local Parameter'!H:H,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))," kg/m^3",IF(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))=""," kg/m^3",INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var rho_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1025,IF(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1025,INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" kg/m^3"&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39">
-        <f>"var l_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("l_tank",'Local Parameter'!$A:$A,0))),42,IF(INDEX('Local Parameter'!E:E,MATCH("l_tank",'Local Parameter'!$A:$A,0))="",42,INDEX('Local Parameter'!E:E,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var l_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),42,IF(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",42,INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="C39">
-        <f>"var l_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("l_tank",'Local Parameter'!$A:$A,0))),42,IF(INDEX('Local Parameter'!F:F,MATCH("l_tank",'Local Parameter'!$A:$A,0))="",42,INDEX('Local Parameter'!F:F,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var l_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),42,IF(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",42,INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="D39">
-        <f>"var l_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("l_tank",'Local Parameter'!$A:$A,0))),42,IF(INDEX('Local Parameter'!G:G,MATCH("l_tank",'Local Parameter'!$A:$A,0))="",42,INDEX('Local Parameter'!G:G,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var l_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),42,IF(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",42,INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="E39">
-        <f>"var l_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("l_tank",'Local Parameter'!$A:$A,0))),42,IF(INDEX('Local Parameter'!H:H,MATCH("l_tank",'Local Parameter'!$A:$A,0))="",42,INDEX('Local Parameter'!H:H,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var l_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),42,IF(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",42,INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40">
-        <f>"var b_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("b_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!E:E,MATCH("b_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!E:E,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var b_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="C40">
-        <f>"var b_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("b_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!F:F,MATCH("b_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!F:F,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var b_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="D40">
-        <f>"var b_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("b_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!G:G,MATCH("b_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!G:G,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var b_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="E40">
-        <f>"var b_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("b_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!H:H,MATCH("b_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!H:H,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var b_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41">
-        <f>"var h_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("h_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!E:E,MATCH("h_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!E:E,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var h_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="C41">
-        <f>"var h_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("h_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!F:F,MATCH("h_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!F:F,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var h_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="D41">
-        <f>"var h_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("h_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!G:G,MATCH("h_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!G:G,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var h_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="E41">
-        <f>"var h_tank = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("h_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!H:H,MATCH("h_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!H:H,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var h_tank = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42">
-        <f>"var eta_deck = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!E:E,MATCH("eta_deck",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!E:E,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var eta_deck = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="C42">
-        <f>"var eta_deck = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!F:F,MATCH("eta_deck",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!F:F,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var eta_deck = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="D42">
-        <f>"var eta_deck = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!G:G,MATCH("eta_deck",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!G:G,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var eta_deck = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="E42">
-        <f>"var eta_deck = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!H:H,MATCH("eta_deck",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!H:H,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var eta_deck = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43">
-        <f>"var eta_overflow = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!E:E,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!E:E,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var eta_overflow = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="C43">
-        <f>"var eta_overflow = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!F:F,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!F:F,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var eta_overflow = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="D43">
-        <f>"var eta_overflow = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!G:G,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!G:G,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var eta_overflow = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="E43">
-        <f>"var eta_overflow = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!H:H,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!H:H,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var eta_overflow = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44">
-        <f>"var C_dp = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("C_dp",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!E:E,MATCH("C_dp",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!E:E,MATCH("C_dp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var C_dp = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="C44">
-        <f>"var C_dp = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("C_dp",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!F:F,MATCH("C_dp",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!F:F,MATCH("C_dp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var C_dp = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="D44">
-        <f>"var C_dp = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("C_dp",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!G:G,MATCH("C_dp",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!G:G,MATCH("C_dp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var C_dp = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="E44">
-        <f>"var C_dp = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("C_dp",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!H:H,MATCH("C_dp",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!H:H,MATCH("C_dp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var C_dp = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45">
-        <f>"var C_ru = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("C_ru",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!E:E,MATCH("C_ru",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!E:E,MATCH("C_ru",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var C_ru = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="C45">
-        <f>"var C_ru = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("C_ru",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!F:F,MATCH("C_ru",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!F:F,MATCH("C_ru",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var C_ru = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="D45">
-        <f>"var C_ru = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("C_ru",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!G:G,MATCH("C_ru",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!G:G,MATCH("C_ru",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var C_ru = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="E45">
-        <f>"var C_ru = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("C_ru",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!H:H,MATCH("C_ru",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!H:H,MATCH("C_ru",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var C_ru = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46">
-        <f>"var p_vp = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("p_vp",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!E:E,MATCH("p_vp",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!E:E,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0)))," N/cm^2",IF(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))=""," N/cm^2",INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var p_vp = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" N/cm^2"&amp;";"</f>
         <v/>
       </c>
       <c r="C46">
-        <f>"var p_vp = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("p_vp",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!F:F,MATCH("p_vp",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!F:F,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0)))," N/cm^2",IF(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))=""," N/cm^2",INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var p_vp = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" N/cm^2"&amp;";"</f>
         <v/>
       </c>
       <c r="D46">
-        <f>"var p_vp = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("p_vp",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!G:G,MATCH("p_vp",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!G:G,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0)))," N/cm^2",IF(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))=""," N/cm^2",INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var p_vp = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" N/cm^2"&amp;";"</f>
         <v/>
       </c>
       <c r="E46">
-        <f>"var p_vp = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("p_vp",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!H:H,MATCH("p_vp",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!H:H,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0)))," N/cm^2",IF(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))=""," N/cm^2",INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var p_vp = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" N/cm^2"&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47">
-        <f>"var GM_full_in = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!E:E,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!E:E,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var GM_full_in = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="C47">
-        <f>"var GM_full_in = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!F:F,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!F:F,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var GM_full_in = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="D47">
-        <f>"var GM_full_in = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!G:G,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!G:G,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var GM_full_in = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="E47">
-        <f>"var GM_full_in = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!H:H,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!H:H,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var GM_full_in = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48">
-        <f>"var k_r_in = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!E:E,MATCH("k_r_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!E:E,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var k_r_in = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="C48">
-        <f>"var k_r_in = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!F:F,MATCH("k_r_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!F:F,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var k_r_in = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="D48">
-        <f>"var k_r_in = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!G:G,MATCH("k_r_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!G:G,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var k_r_in = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
       <c r="E48">
-        <f>"var k_r_in = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!H:H,MATCH("k_r_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!H:H,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;";"</f>
+        <f>"var k_r_in = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49">
-        <f>"var tank_is_ballast = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!E:E,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!E:E,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var tank_is_ballast = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="C49">
-        <f>"var tank_is_ballast = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!F:F,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!F:F,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var tank_is_ballast = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="D49">
-        <f>"var tank_is_ballast = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!G:G,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!G:G,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var tank_is_ballast = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="E49">
-        <f>"var tank_is_ballast = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!H:H,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!H:H,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var tank_is_ballast = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50">
-        <f>"var member_11_17 = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!E:E,MATCH("member_11_17",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!E:E,MATCH("member_11_17",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var member_11_17 = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!E:E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="C50">
-        <f>"var member_11_17 = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!F:F,MATCH("member_11_17",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!F:F,MATCH("member_11_17",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var member_11_17 = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!F:F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="D50">
-        <f>"var member_11_17 = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!G:G,MATCH("member_11_17",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!G:G,MATCH("member_11_17",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var member_11_17 = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!G:G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
       <c r="E50">
-        <f>"var member_11_17 = "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!H:H,MATCH("member_11_17",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!H:H,MATCH("member_11_17",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;";"</f>
+        <f>"var member_11_17 = "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!H:H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;";"</f>
         <v/>
       </c>
     </row>
@@ -4310,7 +4571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4352,7 +4613,7 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>WBT6-d8-mu90</t>
         </is>
@@ -4374,7 +4635,7 @@
         <v/>
       </c>
       <c r="F2">
-        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本项目当前按工况摊平；工具 0.7.0 起支持成员表） |"</f>
+        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 指向成员表 `Tank Data` 的哪一行（指南 §18） |"</f>
         <v/>
       </c>
       <c r="G2">
@@ -4430,31 +4691,31 @@
         <v/>
       </c>
       <c r="T2">
-        <f>"| rho_tank | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),1025,IF(INDEX('Local Parameter'!$E:$E,MATCH("rho_tank",'Local Parameter'!$A:$A,0))="",1025,INDEX('Local Parameter'!$E:$E,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))," kg/m^3",IF(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))=""," kg/m^3",INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;" | 舱数据 |"</f>
+        <f>"| rho_tank | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1025,IF(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1025,INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" kg/m^3"&amp;" | 成员表 Tank Data |"</f>
         <v/>
       </c>
       <c r="U2">
-        <f>"| l_tank / b_tank / h_tank | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("l_tank",'Local Parameter'!$A:$A,0))),42,IF(INDEX('Local Parameter'!$E:$E,MATCH("l_tank",'Local Parameter'!$A:$A,0))="",42,INDEX('Local Parameter'!$E:$E,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("b_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!$E:$E,MATCH("b_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!$E:$E,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("h_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!$E:$E,MATCH("h_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!$E:$E,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;" | Fig. 11 |"</f>
+        <f>"| l_tank / b_tank / h_tank | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),42,IF(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",42,INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | Fig. 11 |"</f>
         <v/>
       </c>
       <c r="V2">
-        <f>"| eta_deck / eta_overflow | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$E:$E,MATCH("eta_deck",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$E:$E,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$E:$E,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$E:$E,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;" | Fig. 12 |"</f>
+        <f>"| eta_deck / eta_overflow | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | Fig. 12 |"</f>
         <v/>
       </c>
       <c r="W2">
-        <f>"| C_dp / C_ru | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("C_dp",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$E:$E,MATCH("C_dp",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$E:$E,MATCH("C_dp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("C_ru",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$E:$E,MATCH("C_ru",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$E:$E,MATCH("C_ru",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;" | 5.7.2(d) |"</f>
+        <f>"| C_dp / C_ru | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" | 5.7.2(d) |"</f>
         <v/>
       </c>
       <c r="X2">
-        <f>"| p_vp | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("p_vp",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$E:$E,MATCH("p_vp",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$E:$E,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0)))," N/cm^2",IF(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))=""," N/cm^2",INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;" | 舱数据 |"</f>
+        <f>"| p_vp | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" N/cm^2"&amp;" | 成员表 Tank Data |"</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>"| GM_full_in / k_r_in | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$E:$E,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$E:$E,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$E:$E,MATCH("k_r_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$E:$E,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;" | 稳性计算书 |"</f>
+        <f>"| GM_full_in / k_r_in | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | 稳性计算书 |"</f>
         <v/>
       </c>
       <c r="Z2">
-        <f>"| tank_is_ballast / member_11_17 | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$E:$E,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$E:$E,MATCH("member_11_17",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$E:$E,MATCH("member_11_17",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;" | Table 3 |"</f>
+        <f>"| tank_is_ballast / member_11_17 | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$E:$E,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" | Table 3 |"</f>
         <v/>
       </c>
       <c r="AA2">
@@ -4479,7 +4740,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>WBT6-d15.059-mu0</t>
         </is>
@@ -4501,7 +4762,7 @@
         <v/>
       </c>
       <c r="F3">
-        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本项目当前按工况摊平；工具 0.7.0 起支持成员表） |"</f>
+        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 指向成员表 `Tank Data` 的哪一行（指南 §18） |"</f>
         <v/>
       </c>
       <c r="G3">
@@ -4557,31 +4818,31 @@
         <v/>
       </c>
       <c r="T3">
-        <f>"| rho_tank | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),1025,IF(INDEX('Local Parameter'!$F:$F,MATCH("rho_tank",'Local Parameter'!$A:$A,0))="",1025,INDEX('Local Parameter'!$F:$F,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))," kg/m^3",IF(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))=""," kg/m^3",INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;" | 舱数据 |"</f>
+        <f>"| rho_tank | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1025,IF(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1025,INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" kg/m^3"&amp;" | 成员表 Tank Data |"</f>
         <v/>
       </c>
       <c r="U3">
-        <f>"| l_tank / b_tank / h_tank | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("l_tank",'Local Parameter'!$A:$A,0))),42,IF(INDEX('Local Parameter'!$F:$F,MATCH("l_tank",'Local Parameter'!$A:$A,0))="",42,INDEX('Local Parameter'!$F:$F,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("b_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!$F:$F,MATCH("b_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!$F:$F,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("h_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!$F:$F,MATCH("h_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!$F:$F,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;" | Fig. 11 |"</f>
+        <f>"| l_tank / b_tank / h_tank | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),42,IF(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",42,INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | Fig. 11 |"</f>
         <v/>
       </c>
       <c r="V3">
-        <f>"| eta_deck / eta_overflow | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$F:$F,MATCH("eta_deck",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$F:$F,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$F:$F,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$F:$F,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;" | Fig. 12 |"</f>
+        <f>"| eta_deck / eta_overflow | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | Fig. 12 |"</f>
         <v/>
       </c>
       <c r="W3">
-        <f>"| C_dp / C_ru | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("C_dp",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$F:$F,MATCH("C_dp",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$F:$F,MATCH("C_dp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("C_ru",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$F:$F,MATCH("C_ru",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$F:$F,MATCH("C_ru",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;" | 5.7.2(d) |"</f>
+        <f>"| C_dp / C_ru | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" | 5.7.2(d) |"</f>
         <v/>
       </c>
       <c r="X3">
-        <f>"| p_vp | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("p_vp",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$F:$F,MATCH("p_vp",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$F:$F,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0)))," N/cm^2",IF(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))=""," N/cm^2",INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;" | 舱数据 |"</f>
+        <f>"| p_vp | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" N/cm^2"&amp;" | 成员表 Tank Data |"</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>"| GM_full_in / k_r_in | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$F:$F,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$F:$F,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$F:$F,MATCH("k_r_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$F:$F,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;" | 稳性计算书 |"</f>
+        <f>"| GM_full_in / k_r_in | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | 稳性计算书 |"</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>"| tank_is_ballast / member_11_17 | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$F:$F,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$F:$F,MATCH("member_11_17",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$F:$F,MATCH("member_11_17",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;" | Table 3 |"</f>
+        <f>"| tank_is_ballast / member_11_17 | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$F:$F,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" | Table 3 |"</f>
         <v/>
       </c>
       <c r="AA3">
@@ -4606,7 +4867,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>WBT7-d20.559-mu90</t>
         </is>
@@ -4628,7 +4889,7 @@
         <v/>
       </c>
       <c r="F4">
-        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本项目当前按工况摊平；工具 0.7.0 起支持成员表） |"</f>
+        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 指向成员表 `Tank Data` 的哪一行（指南 §18） |"</f>
         <v/>
       </c>
       <c r="G4">
@@ -4684,31 +4945,31 @@
         <v/>
       </c>
       <c r="T4">
-        <f>"| rho_tank | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),1025,IF(INDEX('Local Parameter'!$G:$G,MATCH("rho_tank",'Local Parameter'!$A:$A,0))="",1025,INDEX('Local Parameter'!$G:$G,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))," kg/m^3",IF(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))=""," kg/m^3",INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;" | 舱数据 |"</f>
+        <f>"| rho_tank | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1025,IF(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1025,INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" kg/m^3"&amp;" | 成员表 Tank Data |"</f>
         <v/>
       </c>
       <c r="U4">
-        <f>"| l_tank / b_tank / h_tank | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("l_tank",'Local Parameter'!$A:$A,0))),42,IF(INDEX('Local Parameter'!$G:$G,MATCH("l_tank",'Local Parameter'!$A:$A,0))="",42,INDEX('Local Parameter'!$G:$G,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("b_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!$G:$G,MATCH("b_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!$G:$G,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("h_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!$G:$G,MATCH("h_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!$G:$G,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;" | Fig. 11 |"</f>
+        <f>"| l_tank / b_tank / h_tank | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),42,IF(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",42,INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | Fig. 11 |"</f>
         <v/>
       </c>
       <c r="V4">
-        <f>"| eta_deck / eta_overflow | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$G:$G,MATCH("eta_deck",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$G:$G,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$G:$G,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$G:$G,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;" | Fig. 12 |"</f>
+        <f>"| eta_deck / eta_overflow | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | Fig. 12 |"</f>
         <v/>
       </c>
       <c r="W4">
-        <f>"| C_dp / C_ru | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("C_dp",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$G:$G,MATCH("C_dp",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$G:$G,MATCH("C_dp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("C_ru",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$G:$G,MATCH("C_ru",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$G:$G,MATCH("C_ru",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;" | 5.7.2(d) |"</f>
+        <f>"| C_dp / C_ru | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" | 5.7.2(d) |"</f>
         <v/>
       </c>
       <c r="X4">
-        <f>"| p_vp | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("p_vp",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$G:$G,MATCH("p_vp",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$G:$G,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0)))," N/cm^2",IF(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))=""," N/cm^2",INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;" | 舱数据 |"</f>
+        <f>"| p_vp | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" N/cm^2"&amp;" | 成员表 Tank Data |"</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>"| GM_full_in / k_r_in | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$G:$G,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$G:$G,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$G:$G,MATCH("k_r_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$G:$G,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;" | 稳性计算书 |"</f>
+        <f>"| GM_full_in / k_r_in | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | 稳性计算书 |"</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>"| tank_is_ballast / member_11_17 | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$G:$G,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$G:$G,MATCH("member_11_17",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$G:$G,MATCH("member_11_17",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;" | Table 3 |"</f>
+        <f>"| tank_is_ballast / member_11_17 | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$G:$G,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" | Table 3 |"</f>
         <v/>
       </c>
       <c r="AA4">
@@ -4733,7 +4994,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>COT1-d20.559-mu60</t>
         </is>
@@ -4755,7 +5016,7 @@
         <v/>
       </c>
       <c r="F5">
-        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 舱（本项目当前按工况摊平；工具 0.7.0 起支持成员表） |"</f>
+        <f>"| tank_ref | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))&amp;" | 指向成员表 `Tank Data` 的哪一行（指南 §18） |"</f>
         <v/>
       </c>
       <c r="G5">
@@ -4811,31 +5072,31 @@
         <v/>
       </c>
       <c r="T5">
-        <f>"| rho_tank | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("rho_tank",'Local Parameter'!$A:$A,0))),1025,IF(INDEX('Local Parameter'!$H:$H,MATCH("rho_tank",'Local Parameter'!$A:$A,0))="",1025,INDEX('Local Parameter'!$H:$H,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0)))," kg/m^3",IF(INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))=""," kg/m^3",INDEX('Local Parameter'!$D:$D,MATCH("rho_tank",'Local Parameter'!$A:$A,0))))&amp;" | 舱数据 |"</f>
+        <f>"| rho_tank | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1025,IF(INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1025,INDEX('Tank Data'!$B:$B,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" kg/m^3"&amp;" | 成员表 Tank Data |"</f>
         <v/>
       </c>
       <c r="U5">
-        <f>"| l_tank / b_tank / h_tank | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("l_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("l_tank",'Local Parameter'!$A:$A,0))),42,IF(INDEX('Local Parameter'!$H:$H,MATCH("l_tank",'Local Parameter'!$A:$A,0))="",42,INDEX('Local Parameter'!$H:$H,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("l_tank",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("b_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("b_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!$H:$H,MATCH("b_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!$H:$H,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("b_tank",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("h_tank",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("h_tank",'Local Parameter'!$A:$A,0))),32,IF(INDEX('Local Parameter'!$H:$H,MATCH("h_tank",'Local Parameter'!$A:$A,0))="",32,INDEX('Local Parameter'!$H:$H,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("h_tank",'Local Parameter'!$A:$A,0))))&amp;" | Fig. 11 |"</f>
+        <f>"| l_tank / b_tank / h_tank | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),42,IF(INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",42,INDEX('Tank Data'!$C:$C,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$D:$D,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),32,IF(INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",32,INDEX('Tank Data'!$E:$E,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | Fig. 11 |"</f>
         <v/>
       </c>
       <c r="V5">
-        <f>"| eta_deck / eta_overflow | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("eta_deck",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$H:$H,MATCH("eta_deck",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$H:$H,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_deck",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$H:$H,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$H:$H,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("eta_overflow",'Local Parameter'!$A:$A,0))))&amp;" | Fig. 12 |"</f>
+        <f>"| eta_deck / eta_overflow | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$F:$F,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$G:$G,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | Fig. 12 |"</f>
         <v/>
       </c>
       <c r="W5">
-        <f>"| C_dp / C_ru | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("C_dp",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$H:$H,MATCH("C_dp",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$H:$H,MATCH("C_dp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_dp",'Local Parameter'!$A:$A,0)))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("C_ru",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$H:$H,MATCH("C_ru",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$H:$H,MATCH("C_ru",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("C_ru",'Local Parameter'!$A:$A,0)))&amp;" | 5.7.2(d) |"</f>
+        <f>"| C_dp / C_ru | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$H:$H,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$I:$I,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" | 5.7.2(d) |"</f>
         <v/>
       </c>
       <c r="X5">
-        <f>"| p_vp | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("p_vp",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("p_vp",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$H:$H,MATCH("p_vp",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$H:$H,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0)))," N/cm^2",IF(INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))=""," N/cm^2",INDEX('Local Parameter'!$D:$D,MATCH("p_vp",'Local Parameter'!$A:$A,0))))&amp;" | 舱数据 |"</f>
+        <f>"| p_vp | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$J:$J,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" N/cm^2"&amp;" | 成员表 Tank Data |"</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>"| GM_full_in / k_r_in | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$H:$H,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$H:$H,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("GM_full_in",'Local Parameter'!$A:$A,0))))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("k_r_in",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$H:$H,MATCH("k_r_in",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$H:$H,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0)))," m",IF(INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))=""," m",INDEX('Local Parameter'!$D:$D,MATCH("k_r_in",'Local Parameter'!$A:$A,0))))&amp;" | 稳性计算书 |"</f>
+        <f>"| GM_full_in / k_r_in | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$K:$K,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$L:$L,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;" m"&amp;" | 稳性计算书 |"</f>
         <v/>
       </c>
       <c r="Z5">
-        <f>"| tank_is_ballast / member_11_17 | "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),1,IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))="",1,INDEX('Local Parameter'!$H:$H,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("tank_is_ballast",'Local Parameter'!$A:$A,0)))&amp;" / "&amp;IF(ISBLANK(INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$C:$C,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),0,IF(INDEX('Local Parameter'!$H:$H,MATCH("member_11_17",'Local Parameter'!$A:$A,0))="",0,INDEX('Local Parameter'!$H:$H,MATCH("member_11_17",'Local Parameter'!$A:$A,0))))&amp;IF(ISBLANK(INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0))),"",INDEX('Local Parameter'!$D:$D,MATCH("member_11_17",'Local Parameter'!$A:$A,0)))&amp;" | Table 3 |"</f>
+        <f>"| tank_is_ballast / member_11_17 | "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),1,IF(INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",1,INDEX('Tank Data'!$M:$M,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" / "&amp;""&amp;IF(ISBLANK(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))),0,IF(INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))="",0,INDEX('Tank Data'!$N:$N,MATCH(IF(ISBLANK(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))),"WBT6",IF(INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0))="","WBT6",INDEX('Local Parameter'!$H:$H,MATCH("tank_ref",'Local Parameter'!$A:$A,0)))),'Tank Data'!$A:$A,0))))&amp;""&amp;" | Table 3 |"</f>
         <v/>
       </c>
       <c r="AA5">
@@ -4866,7 +5127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6345,7 +6606,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>| tank_ref | {{ tank_ref }} | 舱（本工具无舱作用域，数据按工况摊平） |</t>
+          <t>| tank_ref | {{ tank_ref }} | 指向成员表 `Tank Data` 的哪一行（指南 §18） |</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6746,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>| rho_tank | {{ rho_tank }} | 舱数据 |</t>
+          <t>| rho_tank | {{ rho_tank }} | 成员表 Tank Data |</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6786,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>| p_vp | {{ p_vp }} | 舱数据 |</t>
+          <t>| p_vp | {{ p_vp }} | 成员表 Tank Data |</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6876,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-27 15:22:53</t>
+          <t>2026-09-27 16:02:21</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6888,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>c236aefb8f52</t>
+          <t>89e5e9a6cff2</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6900,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>4dc57fc8ae2d</t>
+          <t>83967e51cf00</t>
         </is>
       </c>
     </row>
